--- a/JsonConverter/ExcelFiles/DNFieldObject.xlsx
+++ b/JsonConverter/ExcelFiles/DNFieldObject.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\UnityBasic_6\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\Unity_2DMainProject\2D_MainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="57">
   <si>
     <t>Harvest</t>
   </si>
@@ -67,9 +67,6 @@
   </si>
   <si>
     <t>harv_potate_1</t>
-  </si>
-  <si>
-    <t>dropItem_gold_1</t>
   </si>
   <si>
     <t>FieldObjectType</t>
@@ -157,7 +154,112 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>Item_Letter_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>dropItem_AncientCoin_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>dropItem_Key_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>dropItem_Letter_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>동전</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>편지</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>열쇠</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>드랍된 동전</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>드랍된 열쇠</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>드랍된 편지</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,5</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_AncientCoin_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Key_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2DPrefab/DropItem_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Letter</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>dropItem_gold_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>Item_Potato_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2DPrefab/DropItem_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Coin</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2DPrefab/DropItem_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Key</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -311,7 +413,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -375,6 +477,7 @@
     <xf numFmtId="49" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -792,7 +895,8 @@
   <dimension ref="A1:R999"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="19.42578125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" style="3" customWidth="1"/>
     <col min="3" max="3" width="19.5703125" style="3" customWidth="1"/>
     <col min="4" max="4" width="50.7109375" style="3" customWidth="1"/>
     <col min="5" max="6" width="50.7109375" style="17" customWidth="1"/>
@@ -809,13 +913,13 @@
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="18"/>
       <c r="F1" s="18"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="12.75">
@@ -850,7 +954,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>7</v>
@@ -859,22 +963,22 @@
         <v>11</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G3" s="14" t="s">
         <v>12</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I3" s="15"/>
     </row>
     <row r="4" spans="1:18" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>0</v>
@@ -883,7 +987,7 @@
         <v>13</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E4" s="20" t="s">
         <v>2</v>
@@ -893,7 +997,7 @@
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I4" s="16"/>
       <c r="J4" s="5"/>
@@ -908,13 +1012,13 @@
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>4</v>
@@ -927,7 +1031,7 @@
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
@@ -948,20 +1052,20 @@
         <v>0</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E6" s="27" t="s">
         <v>2</v>
       </c>
       <c r="F6" s="27" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="G6" s="28"/>
       <c r="H6" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I6" s="28"/>
       <c r="J6" s="28"/>
@@ -976,26 +1080,26 @@
     </row>
     <row r="7" spans="1:18" s="30" customFormat="1" ht="15.75" customHeight="1">
       <c r="A7" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="C7" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="D7" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="E7" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="32" t="s">
+      <c r="F7" s="32" t="s">
         <v>35</v>
-      </c>
-      <c r="F7" s="32" t="s">
-        <v>36</v>
       </c>
       <c r="G7" s="28"/>
       <c r="H7" s="29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I7" s="28"/>
       <c r="J7" s="28"/>
@@ -1009,14 +1113,28 @@
       <c r="R7" s="28"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
+      <c r="A8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>50</v>
+      </c>
       <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
+      <c r="H8" s="33" t="s">
+        <v>55</v>
+      </c>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
@@ -1029,14 +1147,28 @@
       <c r="R8" s="5"/>
     </row>
     <row r="9" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
+      <c r="A9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
+      <c r="H9" s="33" t="s">
+        <v>56</v>
+      </c>
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
@@ -1049,14 +1181,28 @@
       <c r="R9" s="5"/>
     </row>
     <row r="10" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
+      <c r="A10" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
+      <c r="H10" s="33" t="s">
+        <v>52</v>
+      </c>
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>

--- a/JsonConverter/ExcelFiles/DNFieldObject.xlsx
+++ b/JsonConverter/ExcelFiles/DNFieldObject.xlsx
@@ -19,23 +19,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="57">
-  <si>
-    <t>Harvest</t>
-  </si>
-  <si>
-    <t>10,1000</t>
-  </si>
-  <si>
-    <t>10,100</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
   <si>
     <t>int[]</t>
   </si>
   <si>
-    <t>드랍된 금화</t>
-  </si>
-  <si>
     <t>string</t>
   </si>
   <si>
@@ -48,27 +36,15 @@
     <t>캐릭터 고유 ID</t>
   </si>
   <si>
-    <t>Item_Gold_1</t>
-  </si>
-  <si>
-    <t>Item_Corn_1</t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
     <t>IconPath</t>
   </si>
   <si>
-    <t>옥수수</t>
-  </si>
-  <si>
     <t>Id</t>
   </si>
   <si>
-    <t>harv_potate_1</t>
-  </si>
-  <si>
     <t>FieldObjectType</t>
   </si>
   <si>
@@ -84,74 +60,10 @@
     <t>DropItemDataId</t>
   </si>
   <si>
-    <t>감자</t>
-  </si>
-  <si>
-    <t>금화</t>
-  </si>
-  <si>
     <t>DropItem</t>
   </si>
   <si>
-    <t>harv_corn_1</t>
-  </si>
-  <si>
     <t>PrefabPath</t>
-  </si>
-  <si>
-    <t>필드 채집용 옥수수</t>
-  </si>
-  <si>
-    <t>필드 채집용 감자</t>
-  </si>
-  <si>
-    <t>2DPrefab/DropItem_Gold</t>
-  </si>
-  <si>
-    <t>2DPrefab/Harvest_Corn</t>
-  </si>
-  <si>
-    <t>harv_carrot_1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Harvest</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>당근</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>필드 채집용 당근</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>10,100</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Item_Carrot_1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>2DPrefab/Harvest_Potato</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>2DPrefab/Harvest_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Carrot</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Item_Letter_1</t>
@@ -222,14 +134,6 @@
       </rPr>
       <t>Letter</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>dropItem_gold_1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Item_Potato_1</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -352,24 +256,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
+        <fgColor theme="0"/>
+        <bgColor rgb="FFD86DCD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor rgb="FF4D93D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor rgb="FFD86DCD"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -392,28 +296,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -440,9 +329,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -453,31 +339,25 @@
     <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -899,7 +779,7 @@
     <col min="2" max="2" width="19.42578125" style="3" customWidth="1"/>
     <col min="3" max="3" width="19.5703125" style="3" customWidth="1"/>
     <col min="4" max="4" width="50.7109375" style="3" customWidth="1"/>
-    <col min="5" max="6" width="50.7109375" style="17" customWidth="1"/>
+    <col min="5" max="6" width="50.7109375" style="16" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" style="3" customWidth="1"/>
     <col min="8" max="8" width="30.5703125" style="3" customWidth="1"/>
     <col min="9" max="9" width="26.5703125" style="3" customWidth="1"/>
@@ -908,98 +788,98 @@
   <sheetData>
     <row r="1" spans="1:18" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
+        <v>9</v>
+      </c>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="12.75">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="18" t="s">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>1</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2" s="1"/>
     </row>
     <row r="3" spans="1:18" s="13" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="14" t="s">
         <v>14</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>25</v>
       </c>
       <c r="I3" s="15"/>
     </row>
     <row r="4" spans="1:18" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>26</v>
+      <c r="C4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="20" t="s">
-        <v>10</v>
+        <v>25</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="G4" s="5"/>
-      <c r="H4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" s="16"/>
+      <c r="H4" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="5"/>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
@@ -1011,27 +891,27 @@
       <c r="R4" s="5"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A5" s="6" t="s">
-        <v>53</v>
+      <c r="A5" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>9</v>
+      <c r="E5" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="G5" s="5"/>
-      <c r="H5" s="5" t="s">
-        <v>28</v>
+      <c r="H5" s="24" t="s">
+        <v>31</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
@@ -1044,63 +924,49 @@
       <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
     </row>
-    <row r="6" spans="1:18" s="30" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A6" s="26" t="s">
+    <row r="6" spans="1:18" ht="15.75" customHeight="1">
+      <c r="A6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="F6" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="G6" s="28"/>
-      <c r="H6" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" s="28"/>
-      <c r="J6" s="28"/>
-      <c r="K6" s="28"/>
-      <c r="L6" s="28"/>
-      <c r="M6" s="28"/>
-      <c r="N6" s="28"/>
-      <c r="O6" s="28"/>
-      <c r="P6" s="28"/>
-      <c r="Q6" s="28"/>
-      <c r="R6" s="28"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
     </row>
     <row r="7" spans="1:18" s="30" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A7" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="32" t="s">
-        <v>35</v>
-      </c>
+      <c r="A7" s="25"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
       <c r="G7" s="28"/>
-      <c r="H7" s="29" t="s">
-        <v>37</v>
-      </c>
+      <c r="H7" s="29"/>
       <c r="I7" s="28"/>
       <c r="J7" s="28"/>
       <c r="K7" s="28"/>
@@ -1113,28 +979,14 @@
       <c r="R7" s="28"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A8" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>50</v>
-      </c>
+      <c r="A8" s="4"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="4"/>
       <c r="G8" s="5"/>
-      <c r="H8" s="33" t="s">
-        <v>55</v>
-      </c>
+      <c r="H8" s="24"/>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
@@ -1147,28 +999,14 @@
       <c r="R8" s="5"/>
     </row>
     <row r="9" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="A9" s="1"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="1"/>
       <c r="G9" s="5"/>
-      <c r="H9" s="33" t="s">
-        <v>56</v>
-      </c>
+      <c r="H9" s="24"/>
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
@@ -1181,28 +1019,14 @@
       <c r="R9" s="5"/>
     </row>
     <row r="10" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A10" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>38</v>
-      </c>
+      <c r="A10" s="7"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="7"/>
       <c r="G10" s="5"/>
-      <c r="H10" s="33" t="s">
-        <v>52</v>
-      </c>
+      <c r="H10" s="24"/>
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
@@ -1219,8 +1043,8 @@
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
@@ -1239,8 +1063,8 @@
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
@@ -1259,8 +1083,8 @@
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
@@ -1279,8 +1103,8 @@
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
@@ -1299,32 +1123,32 @@
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
     </row>
     <row r="16" spans="1:18" ht="15.75" customHeight="1">
       <c r="A16" s="9"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
     </row>
     <row r="17" spans="1:8" ht="15.75" customHeight="1">
       <c r="A17" s="9"/>
       <c r="B17" s="8"/>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1">
       <c r="A18" s="9"/>
       <c r="B18" s="8"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
     </row>
@@ -1333,48 +1157,48 @@
       <c r="B19" s="8"/>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
     </row>
     <row r="20" spans="1:8" ht="15.75" customHeight="1">
       <c r="A20" s="9"/>
       <c r="B20" s="8"/>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1">
       <c r="A21" s="9"/>
       <c r="B21" s="8"/>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1">
       <c r="A22" s="9"/>
       <c r="B22" s="8"/>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
     </row>
     <row r="23" spans="1:8" ht="15.75" customHeight="1">
       <c r="A23" s="9"/>
       <c r="B23" s="8"/>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
     </row>
     <row r="24" spans="1:8" ht="15.75" customHeight="1">
       <c r="A24" s="9"/>
       <c r="B24" s="8"/>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
       <c r="H24" s="5"/>
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1">
@@ -1382,8 +1206,8 @@
       <c r="B25" s="10"/>
       <c r="C25" s="10"/>
       <c r="D25" s="10"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
       <c r="H25" s="5"/>
     </row>
     <row r="26" spans="1:8" ht="15.75" customHeight="1">
@@ -1391,8 +1215,8 @@
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
       <c r="H26" s="5"/>
     </row>
     <row r="27" spans="1:8" ht="15.75" customHeight="1">
@@ -1400,8 +1224,8 @@
       <c r="B27" s="10"/>
       <c r="C27" s="10"/>
       <c r="D27" s="10"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="24"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
       <c r="H27" s="5"/>
     </row>
     <row r="28" spans="1:8" ht="15.75" customHeight="1">
@@ -1409,56 +1233,56 @@
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
       <c r="D28" s="10"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="24"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
     </row>
     <row r="29" spans="1:8" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="10"/>
       <c r="D29" s="10"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="24"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
     </row>
     <row r="30" spans="1:8" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="10"/>
       <c r="C30" s="10"/>
       <c r="D30" s="10"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="24"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
     </row>
     <row r="31" spans="1:8" ht="15.75" customHeight="1">
       <c r="A31" s="11"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23"/>
     </row>
     <row r="32" spans="1:8" ht="15.75" customHeight="1">
       <c r="A32" s="11"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="25"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="23"/>
     </row>
     <row r="33" spans="1:6" ht="15.75" customHeight="1">
       <c r="A33" s="11"/>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
       <c r="D33" s="11"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="25"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
     </row>
     <row r="34" spans="1:6" ht="15.75" customHeight="1">
       <c r="A34" s="11"/>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="23"/>
     </row>
     <row r="35" spans="1:6" ht="15.75" customHeight="1"/>
     <row r="36" spans="1:6" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/DNFieldObject.xlsx
+++ b/JsonConverter/ExcelFiles/DNFieldObject.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
   <si>
     <t>int[]</t>
   </si>
@@ -164,6 +164,29 @@
       </rPr>
       <t>Key</t>
     </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>dropItem_Churu_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>츄르</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>드랍된 츄르</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Churu_1</t>
+  </si>
+  <si>
+    <t>2DPrefab/DropItem_Churu</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -302,7 +325,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -356,7 +379,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -958,15 +980,29 @@
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
     </row>
-    <row r="7" spans="1:18" s="30" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A7" s="25"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
+    <row r="7" spans="1:18" s="29" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>36</v>
+      </c>
       <c r="G7" s="28"/>
-      <c r="H7" s="29"/>
+      <c r="H7" s="24" t="s">
+        <v>37</v>
+      </c>
       <c r="I7" s="28"/>
       <c r="J7" s="28"/>
       <c r="K7" s="28"/>
@@ -983,7 +1019,9 @@
       <c r="B8" s="6"/>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="20"/>
+      <c r="E8" s="20" t="s">
+        <v>36</v>
+      </c>
       <c r="F8" s="4"/>
       <c r="G8" s="5"/>
       <c r="H8" s="24"/>

--- a/JsonConverter/ExcelFiles/DNFieldObject.xlsx
+++ b/JsonConverter/ExcelFiles/DNFieldObject.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="50">
   <si>
     <t>int[]</t>
   </si>
@@ -187,6 +187,51 @@
   </si>
   <si>
     <t>2DPrefab/DropItem_Churu</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>dropItem_Cat_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>dropItem_Cat_2</t>
+  </si>
+  <si>
+    <t>고양이</t>
+  </si>
+  <si>
+    <t>고양이</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2DPrefab/DropItem_Cat_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2DPrefab/DropItem_Cat_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Cat_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Cat_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>드랍된 고양이 1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>드랍된 고양이 2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1</t>
+  </si>
+  <si>
+    <t>1,1</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1015,16 +1060,28 @@
       <c r="R7" s="28"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A8" s="4"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
+      <c r="A8" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>46</v>
+      </c>
       <c r="E8" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="4"/>
+        <v>49</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>44</v>
+      </c>
       <c r="G8" s="5"/>
-      <c r="H8" s="24"/>
+      <c r="H8" s="24" t="s">
+        <v>42</v>
+      </c>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
@@ -1037,14 +1094,28 @@
       <c r="R8" s="5"/>
     </row>
     <row r="9" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A9" s="1"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="1"/>
+      <c r="A9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="25" t="s">
+        <v>45</v>
+      </c>
       <c r="G9" s="5"/>
-      <c r="H9" s="24"/>
+      <c r="H9" s="24" t="s">
+        <v>43</v>
+      </c>
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
